--- a/output/graficos_nacionales/plot_nacional_serie_p_monto_aps_m_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_monto_aps_m_2021.xlsx
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:18</t>
+    <t xml:space="preserve">2026-10-05 19:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -930,7 +930,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>135422.62</v>
+        <v>135422.63</v>
       </c>
     </row>
     <row r="46">
